--- a/test/fixtures/input/cobertura.xlsx
+++ b/test/fixtures/input/cobertura.xlsx
@@ -490,7 +490,7 @@
         <v>Rio Cuarto</v>
       </c>
       <c r="D5" t="str">
-        <v>5801</v>
+        <v>5800</v>
       </c>
       <c r="E5" t="str">
         <v>Zona Facturacion 3</v>
